--- a/Data/g14.1.xlsx
+++ b/Data/g14.1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D97"/>
+  <dimension ref="A1:D109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4424</v>
+        <v>4823</v>
       </c>
     </row>
     <row r="3">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4370</v>
+        <v>4764</v>
       </c>
     </row>
     <row r="4">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4385</v>
+        <v>4779</v>
       </c>
     </row>
     <row r="5">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4408</v>
+        <v>4805</v>
       </c>
     </row>
     <row r="6">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>4292</v>
+        <v>4679</v>
       </c>
     </row>
     <row r="7">
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>4290</v>
+        <v>4678</v>
       </c>
     </row>
     <row r="8">
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>4285</v>
+        <v>4672</v>
       </c>
     </row>
     <row r="9">
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>4307</v>
+        <v>4695</v>
       </c>
     </row>
     <row r="10">
@@ -627,7 +627,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>4155</v>
+        <v>4529</v>
       </c>
     </row>
     <row r="11">
@@ -647,7 +647,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4099</v>
+        <v>4468</v>
       </c>
     </row>
     <row r="12">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>4107</v>
+        <v>4477</v>
       </c>
     </row>
     <row r="13">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4136</v>
+        <v>4509</v>
       </c>
     </row>
     <row r="14">
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4013</v>
+        <v>4376</v>
       </c>
     </row>
     <row r="15">
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4196</v>
+        <v>4575</v>
       </c>
     </row>
     <row r="16">
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4245</v>
+        <v>4628</v>
       </c>
     </row>
     <row r="17">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>4081</v>
+        <v>4448</v>
       </c>
     </row>
     <row r="18">
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3665</v>
+        <v>3994</v>
       </c>
     </row>
     <row r="19">
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3550</v>
+        <v>3870</v>
       </c>
     </row>
     <row r="20">
@@ -827,7 +827,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>3413</v>
+        <v>3720</v>
       </c>
     </row>
     <row r="21">
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>3300</v>
+        <v>3598</v>
       </c>
     </row>
     <row r="22">
@@ -867,7 +867,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>3175</v>
+        <v>3461</v>
       </c>
     </row>
     <row r="23">
@@ -887,7 +887,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>3194</v>
+        <v>3482</v>
       </c>
     </row>
     <row r="24">
@@ -907,7 +907,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>3307</v>
+        <v>3604</v>
       </c>
     </row>
     <row r="25">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3371</v>
+        <v>3675</v>
       </c>
     </row>
     <row r="26">
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>3247</v>
+        <v>3539</v>
       </c>
     </row>
     <row r="27">
@@ -967,7 +967,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>3241</v>
+        <v>3534</v>
       </c>
     </row>
     <row r="28">
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>3301</v>
+        <v>3598</v>
       </c>
     </row>
     <row r="29">
@@ -1007,7 +1007,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>3324</v>
+        <v>3624</v>
       </c>
     </row>
     <row r="30">
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>3215</v>
+        <v>3504</v>
       </c>
     </row>
     <row r="31">
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>3263</v>
+        <v>3556</v>
       </c>
     </row>
     <row r="32">
@@ -1067,7 +1067,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3256</v>
+        <v>3549</v>
       </c>
     </row>
     <row r="33">
@@ -1087,13 +1087,13 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>3299</v>
+        <v>3596</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1103,17 +1103,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>01/01/2017</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>3000</v>
+        <v>3499</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1123,17 +1123,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>01/04/2017</t>
+          <t>01/04/2025</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>2984</v>
+        <v>3522</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1143,17 +1143,17 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>01/07/2017</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>2930</v>
+        <v>3541</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1163,11 +1163,11 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>01/10/2017</t>
+          <t>01/10/2025</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>3027</v>
+        <v>3625</v>
       </c>
     </row>
     <row r="38">
@@ -1183,11 +1183,11 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>01/01/2018</t>
+          <t>01/01/2017</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>2941</v>
+        <v>3280</v>
       </c>
     </row>
     <row r="39">
@@ -1203,11 +1203,11 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>01/04/2018</t>
+          <t>01/04/2017</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>2925</v>
+        <v>3263</v>
       </c>
     </row>
     <row r="40">
@@ -1223,11 +1223,11 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>01/07/2018</t>
+          <t>01/07/2017</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>2937</v>
+        <v>3206</v>
       </c>
     </row>
     <row r="41">
@@ -1243,11 +1243,11 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>01/10/2018</t>
+          <t>01/10/2017</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>2948</v>
+        <v>3310</v>
       </c>
     </row>
     <row r="42">
@@ -1263,11 +1263,11 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>01/01/2019</t>
+          <t>01/01/2018</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>2840</v>
+        <v>3216</v>
       </c>
     </row>
     <row r="43">
@@ -1283,11 +1283,11 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>01/04/2019</t>
+          <t>01/04/2018</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>2816</v>
+        <v>3199</v>
       </c>
     </row>
     <row r="44">
@@ -1303,11 +1303,11 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>01/07/2019</t>
+          <t>01/07/2018</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>2787</v>
+        <v>3212</v>
       </c>
     </row>
     <row r="45">
@@ -1323,11 +1323,11 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>01/10/2019</t>
+          <t>01/10/2018</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2817</v>
+        <v>3225</v>
       </c>
     </row>
     <row r="46">
@@ -1343,11 +1343,11 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>01/01/2020</t>
+          <t>01/01/2019</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>2734</v>
+        <v>3106</v>
       </c>
     </row>
     <row r="47">
@@ -1363,11 +1363,11 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>01/04/2020</t>
+          <t>01/04/2019</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>2885</v>
+        <v>3079</v>
       </c>
     </row>
     <row r="48">
@@ -1383,11 +1383,11 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>01/07/2020</t>
+          <t>01/07/2019</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>2796</v>
+        <v>3047</v>
       </c>
     </row>
     <row r="49">
@@ -1403,11 +1403,11 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>01/10/2020</t>
+          <t>01/10/2019</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>2716</v>
+        <v>3081</v>
       </c>
     </row>
     <row r="50">
@@ -1423,11 +1423,11 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>01/01/2021</t>
+          <t>01/01/2020</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>2417</v>
+        <v>2990</v>
       </c>
     </row>
     <row r="51">
@@ -1443,11 +1443,11 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>01/04/2021</t>
+          <t>01/04/2020</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>2390</v>
+        <v>3154</v>
       </c>
     </row>
     <row r="52">
@@ -1463,11 +1463,11 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>01/07/2021</t>
+          <t>01/07/2020</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>2300</v>
+        <v>3057</v>
       </c>
     </row>
     <row r="53">
@@ -1483,11 +1483,11 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>01/10/2021</t>
+          <t>01/10/2020</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>2226</v>
+        <v>2969</v>
       </c>
     </row>
     <row r="54">
@@ -1503,11 +1503,11 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>01/01/2022</t>
+          <t>01/01/2021</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>2112</v>
+        <v>2643</v>
       </c>
     </row>
     <row r="55">
@@ -1523,11 +1523,11 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>01/04/2022</t>
+          <t>01/04/2021</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>2110</v>
+        <v>2613</v>
       </c>
     </row>
     <row r="56">
@@ -1543,11 +1543,11 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>01/07/2022</t>
+          <t>01/07/2021</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>2189</v>
+        <v>2515</v>
       </c>
     </row>
     <row r="57">
@@ -1563,11 +1563,11 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>01/10/2022</t>
+          <t>01/10/2021</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>2220</v>
+        <v>2435</v>
       </c>
     </row>
     <row r="58">
@@ -1583,11 +1583,11 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>01/01/2023</t>
+          <t>01/01/2022</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>2178</v>
+        <v>2310</v>
       </c>
     </row>
     <row r="59">
@@ -1603,11 +1603,11 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>01/04/2023</t>
+          <t>01/04/2022</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>2172</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="60">
@@ -1623,11 +1623,11 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>01/07/2023</t>
+          <t>01/07/2022</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>2183</v>
+        <v>2393</v>
       </c>
     </row>
     <row r="61">
@@ -1643,11 +1643,11 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>01/10/2023</t>
+          <t>01/10/2022</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>2209</v>
+        <v>2428</v>
       </c>
     </row>
     <row r="62">
@@ -1663,11 +1663,11 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>01/01/2024</t>
+          <t>01/01/2023</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>2146</v>
+        <v>2382</v>
       </c>
     </row>
     <row r="63">
@@ -1683,11 +1683,11 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>01/04/2024</t>
+          <t>01/04/2023</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>2245</v>
+        <v>2375</v>
       </c>
     </row>
     <row r="64">
@@ -1703,11 +1703,11 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>01/07/2024</t>
+          <t>01/07/2023</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>2207</v>
+        <v>2386</v>
       </c>
     </row>
     <row r="65">
@@ -1723,17 +1723,17 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>01/10/2024</t>
+          <t>01/10/2023</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>2252</v>
+        <v>2414</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1743,17 +1743,17 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>01/01/2017</t>
+          <t>01/01/2024</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>3478</v>
+        <v>2346</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1763,17 +1763,17 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>01/04/2017</t>
+          <t>01/04/2024</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>3326</v>
+        <v>2454</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1783,17 +1783,17 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>01/07/2017</t>
+          <t>01/07/2024</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>3173</v>
+        <v>2414</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1803,17 +1803,17 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>01/10/2017</t>
+          <t>01/10/2024</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>3083</v>
+        <v>2463</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1823,17 +1823,17 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>01/01/2018</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>3107</v>
+        <v>2419</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1843,17 +1843,17 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>01/04/2018</t>
+          <t>01/04/2025</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>2962</v>
+        <v>2424</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1863,17 +1863,17 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>01/07/2018</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>3097</v>
+        <v>2440</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1883,11 +1883,11 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>01/10/2018</t>
+          <t>01/10/2025</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>3021</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="74">
@@ -1903,11 +1903,11 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>01/01/2019</t>
+          <t>01/01/2017</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>2872</v>
+        <v>3807</v>
       </c>
     </row>
     <row r="75">
@@ -1923,11 +1923,11 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>01/04/2019</t>
+          <t>01/04/2017</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>2816</v>
+        <v>3641</v>
       </c>
     </row>
     <row r="76">
@@ -1943,11 +1943,11 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>01/07/2019</t>
+          <t>01/07/2017</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>2785</v>
+        <v>3474</v>
       </c>
     </row>
     <row r="77">
@@ -1963,11 +1963,11 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>01/10/2019</t>
+          <t>01/10/2017</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>2708</v>
+        <v>3375</v>
       </c>
     </row>
     <row r="78">
@@ -1983,11 +1983,11 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>01/01/2020</t>
+          <t>01/01/2018</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>2766</v>
+        <v>3401</v>
       </c>
     </row>
     <row r="79">
@@ -2003,11 +2003,11 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>01/04/2020</t>
+          <t>01/04/2018</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>2945</v>
+        <v>3243</v>
       </c>
     </row>
     <row r="80">
@@ -2023,11 +2023,11 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>01/07/2020</t>
+          <t>01/07/2018</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>2826</v>
+        <v>3391</v>
       </c>
     </row>
     <row r="81">
@@ -2043,11 +2043,11 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>01/10/2020</t>
+          <t>01/10/2018</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>2985</v>
+        <v>3306</v>
       </c>
     </row>
     <row r="82">
@@ -2063,11 +2063,11 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>01/01/2021</t>
+          <t>01/01/2019</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>2445</v>
+        <v>3143</v>
       </c>
     </row>
     <row r="83">
@@ -2083,11 +2083,11 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>01/04/2021</t>
+          <t>01/04/2019</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>2634</v>
+        <v>3082</v>
       </c>
     </row>
     <row r="84">
@@ -2103,11 +2103,11 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>01/07/2021</t>
+          <t>01/07/2019</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>2469</v>
+        <v>3049</v>
       </c>
     </row>
     <row r="85">
@@ -2123,11 +2123,11 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>01/10/2021</t>
+          <t>01/10/2019</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>2399</v>
+        <v>2964</v>
       </c>
     </row>
     <row r="86">
@@ -2143,11 +2143,11 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>01/01/2022</t>
+          <t>01/01/2020</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>2155</v>
+        <v>3028</v>
       </c>
     </row>
     <row r="87">
@@ -2163,11 +2163,11 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>01/04/2022</t>
+          <t>01/04/2020</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>2163</v>
+        <v>3223</v>
       </c>
     </row>
     <row r="88">
@@ -2183,11 +2183,11 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>01/07/2022</t>
+          <t>01/07/2020</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>2262</v>
+        <v>3094</v>
       </c>
     </row>
     <row r="89">
@@ -2203,11 +2203,11 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>01/10/2022</t>
+          <t>01/10/2020</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>2316</v>
+        <v>3267</v>
       </c>
     </row>
     <row r="90">
@@ -2223,11 +2223,11 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>01/01/2023</t>
+          <t>01/01/2021</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>2247</v>
+        <v>2676</v>
       </c>
     </row>
     <row r="91">
@@ -2243,11 +2243,11 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>01/04/2023</t>
+          <t>01/04/2021</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>2295</v>
+        <v>2884</v>
       </c>
     </row>
     <row r="92">
@@ -2263,11 +2263,11 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>01/07/2023</t>
+          <t>01/07/2021</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>2215</v>
+        <v>2702</v>
       </c>
     </row>
     <row r="93">
@@ -2283,11 +2283,11 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>01/10/2023</t>
+          <t>01/10/2021</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>2185</v>
+        <v>2626</v>
       </c>
     </row>
     <row r="94">
@@ -2303,11 +2303,11 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>01/01/2024</t>
+          <t>01/01/2022</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>2147</v>
+        <v>2359</v>
       </c>
     </row>
     <row r="95">
@@ -2323,11 +2323,11 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>01/04/2024</t>
+          <t>01/04/2022</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>2265</v>
+        <v>2368</v>
       </c>
     </row>
     <row r="96">
@@ -2343,11 +2343,11 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>01/07/2024</t>
+          <t>01/07/2022</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>2291</v>
+        <v>2475</v>
       </c>
     </row>
     <row r="97">
@@ -2363,11 +2363,251 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
+          <t>01/10/2022</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>2535</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Rendimento médio mensal real das pessoas de 14 anos ou mais de idade ocupadas na semana de referência com rendimento de trabalho, habitualmente recebido em todos os trabalhos</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>01/01/2023</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>2459</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Rendimento médio mensal real das pessoas de 14 anos ou mais de idade ocupadas na semana de referência com rendimento de trabalho, habitualmente recebido em todos os trabalhos</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>01/04/2023</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>2513</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Rendimento médio mensal real das pessoas de 14 anos ou mais de idade ocupadas na semana de referência com rendimento de trabalho, habitualmente recebido em todos os trabalhos</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>01/07/2023</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>2424</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Rendimento médio mensal real das pessoas de 14 anos ou mais de idade ocupadas na semana de referência com rendimento de trabalho, habitualmente recebido em todos os trabalhos</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>01/10/2023</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>2392</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Rendimento médio mensal real das pessoas de 14 anos ou mais de idade ocupadas na semana de referência com rendimento de trabalho, habitualmente recebido em todos os trabalhos</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>01/01/2024</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>2350</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Rendimento médio mensal real das pessoas de 14 anos ou mais de idade ocupadas na semana de referência com rendimento de trabalho, habitualmente recebido em todos os trabalhos</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>01/04/2024</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>2479</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Rendimento médio mensal real das pessoas de 14 anos ou mais de idade ocupadas na semana de referência com rendimento de trabalho, habitualmente recebido em todos os trabalhos</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>01/07/2024</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>2508</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Rendimento médio mensal real das pessoas de 14 anos ou mais de idade ocupadas na semana de referência com rendimento de trabalho, habitualmente recebido em todos os trabalhos</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
           <t>01/10/2024</t>
         </is>
       </c>
-      <c r="D97" t="n">
-        <v>2477</v>
+      <c r="D105" t="n">
+        <v>2711</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Rendimento médio mensal real das pessoas de 14 anos ou mais de idade ocupadas na semana de referência com rendimento de trabalho, habitualmente recebido em todos os trabalhos</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>2592</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Rendimento médio mensal real das pessoas de 14 anos ou mais de idade ocupadas na semana de referência com rendimento de trabalho, habitualmente recebido em todos os trabalhos</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>01/04/2025</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>2546</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Rendimento médio mensal real das pessoas de 14 anos ou mais de idade ocupadas na semana de referência com rendimento de trabalho, habitualmente recebido em todos os trabalhos</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>01/07/2025</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>2835</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Rendimento médio mensal real das pessoas de 14 anos ou mais de idade ocupadas na semana de referência com rendimento de trabalho, habitualmente recebido em todos os trabalhos</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>01/10/2025</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>2807</v>
       </c>
     </row>
   </sheetData>
